--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -14,10 +14,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:P5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="12" width="18" customWidth="1"/>
+    <col min="2" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33,37 +33,72 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21.06.2026</t>
+          <t>22.06.2026</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>22.06.2026</t>
+          <t>23.06.2026</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>23.06.2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>25.06.2026</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>26.06.2026</t>
+          <t>27.06.2026</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>27.06.2026</t>
+          <t>29.06.2026</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>04.07.2026</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
         </is>
       </c>
     </row>
@@ -84,25 +119,46 @@
         <v>132</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D3">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E3">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="F3">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="G3">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H3">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="I3">
-        <v>88</v>
+        <v>200</v>
+      </c>
+      <c r="J3">
+        <v>236</v>
+      </c>
+      <c r="K3">
+        <v>211</v>
+      </c>
+      <c r="L3">
+        <v>216</v>
+      </c>
+      <c r="M3">
+        <v>360</v>
+      </c>
+      <c r="N3">
+        <v>134</v>
+      </c>
+      <c r="O3">
+        <v>241</v>
+      </c>
+      <c r="P3">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -122,25 +178,46 @@
         <v>132</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D5">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="F5">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="G5">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H5">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="I5">
-        <v>88</v>
+        <v>200</v>
+      </c>
+      <c r="J5">
+        <v>236</v>
+      </c>
+      <c r="K5">
+        <v>211</v>
+      </c>
+      <c r="L5">
+        <v>216</v>
+      </c>
+      <c r="M5">
+        <v>360</v>
+      </c>
+      <c r="N5">
+        <v>134</v>
+      </c>
+      <c r="O5">
+        <v>241</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -149,10 +226,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:S7"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="12" width="18" customWidth="1"/>
+    <col min="2" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -211,6 +288,46 @@
           <t>29.06.2026</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>04.07.2026</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -219,34 +336,58 @@
         </is>
       </c>
       <c r="B2">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="C2">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>392</v>
+      </c>
+      <c r="E2">
+        <v>442</v>
+      </c>
+      <c r="F2">
+        <v>499</v>
+      </c>
+      <c r="G2">
+        <v>395</v>
+      </c>
+      <c r="H2">
+        <v>359</v>
+      </c>
+      <c r="I2">
+        <v>323</v>
+      </c>
+      <c r="J2">
+        <v>51</v>
+      </c>
+      <c r="K2">
+        <v>770</v>
+      </c>
+      <c r="L2">
+        <v>842</v>
+      </c>
+      <c r="M2">
+        <v>775</v>
+      </c>
+      <c r="N2">
+        <v>772</v>
+      </c>
+      <c r="O2">
+        <v>518</v>
+      </c>
+      <c r="P2">
+        <v>409</v>
+      </c>
+      <c r="Q2">
         <v>30</v>
       </c>
-      <c r="D2">
-        <v>381</v>
-      </c>
-      <c r="E2">
-        <v>406</v>
-      </c>
-      <c r="F2">
-        <v>471</v>
-      </c>
-      <c r="G2">
-        <v>367</v>
-      </c>
-      <c r="H2">
-        <v>345</v>
-      </c>
-      <c r="I2">
-        <v>309</v>
-      </c>
-      <c r="J2">
-        <v>40</v>
-      </c>
-      <c r="K2">
-        <v>269</v>
+      <c r="R2">
+        <v>591</v>
+      </c>
+      <c r="S2">
+        <v>123</v>
       </c>
     </row>
     <row r="3">
@@ -256,25 +397,25 @@
         </is>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>11</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>14</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -283,6 +424,30 @@
         <v>12</v>
       </c>
       <c r="K3">
+        <v>49</v>
+      </c>
+      <c r="L3">
+        <v>44</v>
+      </c>
+      <c r="M3">
+        <v>29</v>
+      </c>
+      <c r="N3">
+        <v>45</v>
+      </c>
+      <c r="O3">
+        <v>18</v>
+      </c>
+      <c r="P3">
+        <v>26</v>
+      </c>
+      <c r="Q3">
+        <v>17</v>
+      </c>
+      <c r="R3">
+        <v>30</v>
+      </c>
+      <c r="S3">
         <v>5</v>
       </c>
     </row>
@@ -292,9 +457,6 @@
           <t>Целевая квота</t>
         </is>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -315,18 +477,42 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>7</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>21</v>
+      </c>
+      <c r="M5">
+        <v>28</v>
+      </c>
+      <c r="N5">
+        <v>29</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>11</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
         <v>11</v>
       </c>
     </row>
@@ -352,16 +538,40 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>7</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>38</v>
+      </c>
+      <c r="M6">
+        <v>19</v>
+      </c>
+      <c r="N6">
+        <v>31</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>15</v>
+      </c>
+      <c r="Q6">
+        <v>7</v>
+      </c>
+      <c r="R6">
+        <v>13</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -371,34 +581,58 @@
         </is>
       </c>
       <c r="B7">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="E7">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="F7">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="G7">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="H7">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="I7">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="J7">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="K7">
-        <v>285</v>
+        <v>852</v>
+      </c>
+      <c r="L7">
+        <v>945</v>
+      </c>
+      <c r="M7">
+        <v>851</v>
+      </c>
+      <c r="N7">
+        <v>877</v>
+      </c>
+      <c r="O7">
+        <v>544</v>
+      </c>
+      <c r="P7">
+        <v>461</v>
+      </c>
+      <c r="Q7">
+        <v>58</v>
+      </c>
+      <c r="R7">
+        <v>645</v>
+      </c>
+      <c r="S7">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -410,7 +644,7 @@
   <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="12" width="18" customWidth="1"/>
+    <col min="2" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,7 +666,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>3309</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="3">
@@ -442,7 +676,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>448</v>
+        <v>1526</v>
       </c>
     </row>
   </sheetData>
@@ -454,7 +688,7 @@
   <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="12" width="18" customWidth="1"/>
+    <col min="2" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +710,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>448</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +720,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>2861</v>
+        <v>7049</v>
       </c>
     </row>
   </sheetData>
@@ -498,7 +732,7 @@
   <dimension ref="A1:D6"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="12" width="18" customWidth="1"/>
+    <col min="2" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,16 +765,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.40.03.01</t>
+          <t>40.03.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Код: 5.40.03.01</t>
+          <t>Код: 40.03.01</t>
         </is>
       </c>
       <c r="D2">
-        <v>468</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="3">
@@ -551,16 +785,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.38.03.01</t>
+          <t>38.03.01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Код: 5.38.03.01</t>
+          <t>Код: 38.03.01</t>
         </is>
       </c>
       <c r="D3">
-        <v>232</v>
+        <v>686</v>
       </c>
     </row>
     <row r="4">
@@ -571,56 +805,56 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.44.03.05</t>
+          <t>44.03.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Код: 6.44.03.05</t>
+          <t>Код: 44.03.05</t>
         </is>
       </c>
       <c r="D4">
-        <v>185</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Государственное и муниципальное управление</t>
+          <t>Судебная и прокурорская деятельность</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.38.03.04</t>
+          <t>40.05.04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Код: 5.38.03.04</t>
+          <t>Код: 40.05.04</t>
         </is>
       </c>
       <c r="D5">
-        <v>144</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Судебная и прокурорская деятельность</t>
+          <t>Государственное и муниципальное управление</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.40.05.04</t>
+          <t>38.03.04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Код: 5.40.05.04</t>
+          <t>Код: 38.03.04</t>
         </is>
       </c>
       <c r="D6">
-        <v>132</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -632,7 +866,7 @@
   <dimension ref="A1:D6"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="12" width="18" customWidth="1"/>
+    <col min="2" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -660,17 +894,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Организация работы с молодежью</t>
+          <t>Социология</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.39.04.03</t>
+          <t>39.04.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Код: 5.39.04.03</t>
+          <t>Код: 39.04.01</t>
         </is>
       </c>
       <c r="D2">
@@ -680,37 +914,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Технологические машины и оборудование</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.15.04.02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Код: 2.15.04.02</t>
+          <t>4.3.2 Электротехнологии, электрооборудование и энергоснабжение агропромышленного комплекса</t>
         </is>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>История</t>
+          <t>Гидромелиорация</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.46.04.01</t>
+          <t>35.04.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Код: 7.46.04.01</t>
+          <t>Код: 35.04.10</t>
         </is>
       </c>
       <c r="D4">
@@ -720,17 +944,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Культурология</t>
+          <t>Журналистика</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.51.04.01</t>
+          <t>42.04.02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Код: 8.51.04.01</t>
+          <t>Код: 42.04.02</t>
         </is>
       </c>
       <c r="D5">
@@ -740,17 +964,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Садоводство</t>
+          <t>Культурология</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.35.04.05</t>
+          <t>51.04.01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Код: 4.35.04.05</t>
+          <t>Код: 51.04.01</t>
         </is>
       </c>
       <c r="D6">

--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -158,7 +158,7 @@
         <v>241</v>
       </c>
       <c r="P3">
-        <v>100</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4">
@@ -217,7 +217,7 @@
         <v>241</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="32" width="18" customWidth="1"/>
@@ -101,6 +101,11 @@
           <t>07.07.2026</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -158,7 +163,10 @@
         <v>241</v>
       </c>
       <c r="P3">
-        <v>197</v>
+        <v>194</v>
+      </c>
+      <c r="Q3">
+        <v>129</v>
       </c>
     </row>
     <row r="4">
@@ -217,7 +225,10 @@
         <v>241</v>
       </c>
       <c r="P5">
-        <v>197</v>
+        <v>194</v>
+      </c>
+      <c r="Q5">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:W5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="32" width="18" customWidth="1"/>
@@ -106,6 +106,36 @@
           <t>08.07.2026</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>11.07.2026</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -168,6 +198,24 @@
       <c r="Q3">
         <v>129</v>
       </c>
+      <c r="R3">
+        <v>169</v>
+      </c>
+      <c r="S3">
+        <v>153</v>
+      </c>
+      <c r="T3">
+        <v>111</v>
+      </c>
+      <c r="U3">
+        <v>237</v>
+      </c>
+      <c r="V3">
+        <v>218</v>
+      </c>
+      <c r="W3">
+        <v>221</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -229,6 +277,24 @@
       </c>
       <c r="Q5">
         <v>129</v>
+      </c>
+      <c r="R5">
+        <v>169</v>
+      </c>
+      <c r="S5">
+        <v>153</v>
+      </c>
+      <c r="T5">
+        <v>111</v>
+      </c>
+      <c r="U5">
+        <v>237</v>
+      </c>
+      <c r="V5">
+        <v>218</v>
+      </c>
+      <c r="W5">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +743,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>8575</v>
+        <v>13201</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +753,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1526</v>
+        <v>2414</v>
       </c>
     </row>
   </sheetData>
@@ -721,7 +787,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>1526</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="3">
@@ -731,7 +797,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>7049</v>
+        <v>10787</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:AA5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="32" width="18" customWidth="1"/>
@@ -136,6 +136,26 @@
           <t>15.07.2026</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>18.07.2026</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -216,6 +236,18 @@
       <c r="W3">
         <v>221</v>
       </c>
+      <c r="X3">
+        <v>205</v>
+      </c>
+      <c r="Y3">
+        <v>198</v>
+      </c>
+      <c r="Z3">
+        <v>95</v>
+      </c>
+      <c r="AA3">
+        <v>367</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -295,6 +327,18 @@
       </c>
       <c r="W5">
         <v>221</v>
+      </c>
+      <c r="X5">
+        <v>205</v>
+      </c>
+      <c r="Y5">
+        <v>198</v>
+      </c>
+      <c r="Z5">
+        <v>95</v>
+      </c>
+      <c r="AA5">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +787,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>13201</v>
+        <v>15791</v>
       </c>
     </row>
     <row r="3">
@@ -753,7 +797,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>2414</v>
+        <v>3021</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +831,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>2414</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="3">
@@ -797,7 +841,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>10787</v>
+        <v>12770</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AK5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="32" width="18" customWidth="1"/>
@@ -156,6 +156,56 @@
           <t>20.07.2026</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -246,7 +296,37 @@
         <v>95</v>
       </c>
       <c r="AA3">
-        <v>367</v>
+        <v>373</v>
+      </c>
+      <c r="AB3">
+        <v>25</v>
+      </c>
+      <c r="AC3">
+        <v>10</v>
+      </c>
+      <c r="AD3">
+        <v>139</v>
+      </c>
+      <c r="AE3">
+        <v>47</v>
+      </c>
+      <c r="AF3">
+        <v>14</v>
+      </c>
+      <c r="AG3">
+        <v>37</v>
+      </c>
+      <c r="AH3">
+        <v>-2</v>
+      </c>
+      <c r="AI3">
+        <v>25</v>
+      </c>
+      <c r="AJ3">
+        <v>8</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -338,7 +418,37 @@
         <v>95</v>
       </c>
       <c r="AA5">
-        <v>367</v>
+        <v>373</v>
+      </c>
+      <c r="AB5">
+        <v>25</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>139</v>
+      </c>
+      <c r="AE5">
+        <v>47</v>
+      </c>
+      <c r="AF5">
+        <v>14</v>
+      </c>
+      <c r="AG5">
+        <v>37</v>
+      </c>
+      <c r="AH5">
+        <v>-2</v>
+      </c>
+      <c r="AI5">
+        <v>25</v>
+      </c>
+      <c r="AJ5">
+        <v>8</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +897,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>15791</v>
+        <v>16767</v>
       </c>
     </row>
     <row r="3">
@@ -797,7 +907,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3021</v>
+        <v>3629</v>
       </c>
     </row>
   </sheetData>
@@ -831,7 +941,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>3021</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="3">
@@ -841,7 +951,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>12770</v>
+        <v>13138</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/manual-dashboard-data.xlsx
+++ b/DATA/manual-dashboard-data.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AP5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="32" width="18" customWidth="1"/>
@@ -206,6 +206,31 @@
           <t>07.08.2026</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -326,7 +351,22 @@
         <v>8</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AL3">
+        <v>80</v>
+      </c>
+      <c r="AM3">
+        <v>35</v>
+      </c>
+      <c r="AN3">
+        <v>33</v>
+      </c>
+      <c r="AO3">
+        <v>27</v>
+      </c>
+      <c r="AP3">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -448,7 +488,22 @@
         <v>8</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AL5">
+        <v>80</v>
+      </c>
+      <c r="AM5">
+        <v>35</v>
+      </c>
+      <c r="AN5">
+        <v>33</v>
+      </c>
+      <c r="AO5">
+        <v>27</v>
+      </c>
+      <c r="AP5">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +952,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>16767</v>
+        <v>17856</v>
       </c>
     </row>
     <row r="3">
@@ -907,7 +962,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3629</v>
+        <v>3901</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +996,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>3629</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="3">
@@ -951,7 +1006,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>13138</v>
+        <v>13955</v>
       </c>
     </row>
   </sheetData>
